--- a/data/hex_xlsx/OUT1V.HE.xlsx
+++ b/data/hex_xlsx/OUT1V.HE.xlsx
@@ -16242,13 +16242,34 @@
       <c r="Q77" s="15">
         <v>15996.22</v>
       </c>
-      <c r="R77" s="15"/>
-      <c r="S77" s="15"/>
-      <c r="T77" s="15"/>
-      <c r="U77" s="15"/>
-      <c r="V77" s="15"/>
-      <c r="W77" s="15"/>
-      <c r="X77" s="15"/>
+      <c r="R77" s="15">
+        <f t="shared" ref="R77:X77" si="1">R78+R79</f>
+        <v>17408.73</v>
+      </c>
+      <c r="S77" s="15">
+        <f t="shared" si="1"/>
+        <v>19678.4</v>
+      </c>
+      <c r="T77" s="15">
+        <f t="shared" si="1"/>
+        <v>15698.75</v>
+      </c>
+      <c r="U77" s="15">
+        <f t="shared" si="1"/>
+        <v>17025.23</v>
+      </c>
+      <c r="V77" s="15">
+        <f t="shared" si="1"/>
+        <v>16966.74</v>
+      </c>
+      <c r="W77" s="15">
+        <f t="shared" si="1"/>
+        <v>22604.69</v>
+      </c>
+      <c r="X77" s="15">
+        <f t="shared" si="1"/>
+        <v>22395.24</v>
+      </c>
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
@@ -19040,43 +19061,103 @@
       <c r="U132" s="15"/>
       <c r="V132" s="15"/>
       <c r="W132" s="15"/>
-      <c r="X132" s="18">
-        <v>8276.5</v>
-      </c>
+      <c r="X132" s="18"/>
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="B133" s="15"/>
-      <c r="C133" s="15"/>
-      <c r="D133" s="15"/>
-      <c r="E133" s="15"/>
-      <c r="F133" s="15"/>
-      <c r="G133" s="15"/>
-      <c r="H133" s="15"/>
-      <c r="I133" s="15"/>
-      <c r="J133" s="15"/>
-      <c r="K133" s="15"/>
-      <c r="L133" s="15"/>
-      <c r="M133" s="15"/>
-      <c r="N133" s="18">
+      <c r="B133" s="15">
+        <f t="shared" ref="B133:Q133" si="2">B132-B140-B138</f>
+        <v>767.91</v>
+      </c>
+      <c r="C133" s="15">
+        <f t="shared" si="2"/>
+        <v>2565.2</v>
+      </c>
+      <c r="D133" s="15">
+        <f t="shared" si="2"/>
+        <v>592.8</v>
+      </c>
+      <c r="E133" s="15">
+        <f t="shared" si="2"/>
+        <v>1090.36</v>
+      </c>
+      <c r="F133" s="15">
+        <f t="shared" si="2"/>
+        <v>800.92</v>
+      </c>
+      <c r="G133" s="15">
+        <f t="shared" si="2"/>
+        <v>2440.95</v>
+      </c>
+      <c r="H133" s="15">
+        <f t="shared" si="2"/>
+        <v>3906.71</v>
+      </c>
+      <c r="I133" s="15">
+        <f t="shared" si="2"/>
+        <v>5033.1</v>
+      </c>
+      <c r="J133" s="15">
+        <f t="shared" si="2"/>
+        <v>4922.56</v>
+      </c>
+      <c r="K133" s="15">
+        <f t="shared" si="2"/>
+        <v>3568.48</v>
+      </c>
+      <c r="L133" s="15">
+        <f t="shared" si="2"/>
+        <v>4982.41</v>
+      </c>
+      <c r="M133" s="15">
+        <f t="shared" si="2"/>
+        <v>4862.92</v>
+      </c>
+      <c r="N133" s="15">
+        <f t="shared" si="2"/>
         <v>7262.48</v>
       </c>
-      <c r="O133" s="18">
-        <v>5167.24</v>
-      </c>
-      <c r="P133" s="18">
+      <c r="O133" s="15">
+        <f t="shared" si="2"/>
+        <v>5167.23</v>
+      </c>
+      <c r="P133" s="15">
+        <f t="shared" si="2"/>
         <v>7628.39</v>
       </c>
-      <c r="Q133" s="15"/>
-      <c r="R133" s="15"/>
-      <c r="S133" s="15"/>
-      <c r="T133" s="15"/>
-      <c r="U133" s="15"/>
-      <c r="V133" s="15"/>
-      <c r="W133" s="15"/>
-      <c r="X133" s="15"/>
+      <c r="Q133" s="15">
+        <f t="shared" si="2"/>
+        <v>7242.69</v>
+      </c>
+      <c r="R133" s="15">
+        <f t="shared" ref="R133:W133" si="3">R141+R137+R135+R134-R138</f>
+        <v>5266.58</v>
+      </c>
+      <c r="S133" s="15">
+        <f t="shared" si="3"/>
+        <v>4786.12</v>
+      </c>
+      <c r="T133" s="15">
+        <f t="shared" si="3"/>
+        <v>3250.75</v>
+      </c>
+      <c r="U133" s="15">
+        <f t="shared" si="3"/>
+        <v>5115.8</v>
+      </c>
+      <c r="V133" s="15">
+        <f t="shared" si="3"/>
+        <v>3920.32</v>
+      </c>
+      <c r="W133" s="15">
+        <f t="shared" si="3"/>
+        <v>8995.74</v>
+      </c>
+      <c r="X133" s="18">
+        <v>8276.5</v>
+      </c>
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
